--- a/정기/BM/각성 절멸타 수치/육성골드계산.xlsx
+++ b/정기/BM/각성 절멸타 수치/육성골드계산.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JJG\엑셀\정기\서든\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JJG\엑셀\정기\BM\각성 절멸타 수치\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D788031-423E-4F63-BE47-490A79B995B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0FC337C-D811-4B81-89A5-264F3FA20121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14865" yWindow="45" windowWidth="16185" windowHeight="15480" firstSheet="1" activeTab="2" xr2:uid="{A99CFEC2-60A2-4309-B5ED-2C883047AF44}"/>
+    <workbookView xWindow="9600" yWindow="420" windowWidth="25335" windowHeight="15480" firstSheet="1" activeTab="4" xr2:uid="{A99CFEC2-60A2-4309-B5ED-2C883047AF44}"/>
   </bookViews>
   <sheets>
     <sheet name="육성1 골드" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="132">
   <si>
     <t xml:space="preserve"> </t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -529,6 +529,10 @@
     <t>ㅇ</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>초항</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -846,10 +850,10 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6615,7 +6619,7 @@
         <v>7837.5</v>
       </c>
       <c r="Z4">
-        <f>T4*W4*0.6</f>
+        <f t="shared" ref="Z4:Z38" si="1">T4*W4*0.6</f>
         <v>6412.5</v>
       </c>
       <c r="AA4">
@@ -6623,7 +6627,7 @@
         <v>7837.5</v>
       </c>
       <c r="AC4">
-        <f>V4*W4*0.6</f>
+        <f t="shared" ref="AC4:AC38" si="2">V4*W4*0.6</f>
         <v>14250</v>
       </c>
       <c r="AE4">
@@ -6697,7 +6701,7 @@
         <v>60000</v>
       </c>
       <c r="V5">
-        <f t="shared" ref="V5:V23" si="1">U5+T5</f>
+        <f t="shared" ref="V5:V23" si="3">U5+T5</f>
         <v>100000</v>
       </c>
       <c r="W5" s="30">
@@ -6710,15 +6714,15 @@
         <v>34200</v>
       </c>
       <c r="Z5">
-        <f>T5*W5*0.6</f>
+        <f t="shared" si="1"/>
         <v>22800</v>
       </c>
       <c r="AA5">
-        <f t="shared" ref="Y5:AA23" si="2">U5*W5*0.6</f>
+        <f t="shared" ref="AA5:AA23" si="4">U5*W5*0.6</f>
         <v>34200</v>
       </c>
       <c r="AC5">
-        <f>V5*W5*0.6</f>
+        <f t="shared" si="2"/>
         <v>57000</v>
       </c>
       <c r="AE5">
@@ -6772,27 +6776,27 @@
         <v>3</v>
       </c>
       <c r="P6">
-        <f t="shared" ref="P6:P23" si="3">R5</f>
+        <f t="shared" ref="P6:P23" si="5">R5</f>
         <v>350</v>
       </c>
       <c r="Q6">
-        <f t="shared" ref="Q6:Q23" si="4">P6+(M6-L6)*O6</f>
+        <f t="shared" ref="Q6:Q23" si="6">P6+(M6-L6)*O6</f>
         <v>500</v>
       </c>
       <c r="R6">
-        <f t="shared" ref="R6:R23" si="5">Q6+(N6-M6)*O6</f>
+        <f t="shared" ref="R6:R23" si="7">Q6+(N6-M6)*O6</f>
         <v>650</v>
       </c>
       <c r="T6">
-        <f t="shared" ref="T6:T23" si="6">50*(P6+Q6)/2*4</f>
+        <f t="shared" ref="T6:T23" si="8">50*(P6+Q6)/2*4</f>
         <v>85000</v>
       </c>
       <c r="U6">
-        <f t="shared" ref="U6:U23" si="7">50*(R6+Q6)/2*4</f>
+        <f t="shared" ref="U6:U23" si="9">50*(R6+Q6)/2*4</f>
         <v>115000</v>
       </c>
       <c r="V6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>200000</v>
       </c>
       <c r="W6" s="30">
@@ -6805,15 +6809,15 @@
         <v>62100</v>
       </c>
       <c r="Z6">
-        <f>T6*W6*0.6</f>
+        <f t="shared" si="1"/>
         <v>45900</v>
       </c>
       <c r="AA6">
+        <f t="shared" si="4"/>
+        <v>62100</v>
+      </c>
+      <c r="AC6">
         <f t="shared" si="2"/>
-        <v>62100</v>
-      </c>
-      <c r="AC6">
-        <f>V6*W6*0.6</f>
         <v>108000</v>
       </c>
       <c r="AE6">
@@ -6867,27 +6871,27 @@
         <v>4</v>
       </c>
       <c r="P7">
+        <f t="shared" si="5"/>
+        <v>650</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="6"/>
+        <v>850</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="7"/>
+        <v>1050</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="8"/>
+        <v>150000</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="9"/>
+        <v>190000</v>
+      </c>
+      <c r="V7">
         <f t="shared" si="3"/>
-        <v>650</v>
-      </c>
-      <c r="Q7">
-        <f t="shared" si="4"/>
-        <v>850</v>
-      </c>
-      <c r="R7">
-        <f t="shared" si="5"/>
-        <v>1050</v>
-      </c>
-      <c r="T7">
-        <f t="shared" si="6"/>
-        <v>150000</v>
-      </c>
-      <c r="U7">
-        <f t="shared" si="7"/>
-        <v>190000</v>
-      </c>
-      <c r="V7">
-        <f t="shared" si="1"/>
         <v>340000</v>
       </c>
       <c r="W7" s="30">
@@ -6900,15 +6904,15 @@
         <v>102600</v>
       </c>
       <c r="Z7">
-        <f>T7*W7*0.6</f>
+        <f t="shared" si="1"/>
         <v>81000</v>
       </c>
       <c r="AA7">
+        <f t="shared" si="4"/>
+        <v>102600</v>
+      </c>
+      <c r="AC7">
         <f t="shared" si="2"/>
-        <v>102600</v>
-      </c>
-      <c r="AC7">
-        <f>V7*W7*0.6</f>
         <v>183600</v>
       </c>
       <c r="AE7">
@@ -6962,27 +6966,27 @@
         <v>5</v>
       </c>
       <c r="P8">
+        <f t="shared" si="5"/>
+        <v>1050</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="6"/>
+        <v>1300</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="7"/>
+        <v>1550</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="8"/>
+        <v>235000</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="9"/>
+        <v>285000</v>
+      </c>
+      <c r="V8">
         <f t="shared" si="3"/>
-        <v>1050</v>
-      </c>
-      <c r="Q8">
-        <f t="shared" si="4"/>
-        <v>1300</v>
-      </c>
-      <c r="R8">
-        <f t="shared" si="5"/>
-        <v>1550</v>
-      </c>
-      <c r="T8">
-        <f t="shared" si="6"/>
-        <v>235000</v>
-      </c>
-      <c r="U8">
-        <f t="shared" si="7"/>
-        <v>285000</v>
-      </c>
-      <c r="V8">
-        <f t="shared" si="1"/>
         <v>520000</v>
       </c>
       <c r="W8" s="29">
@@ -6995,15 +6999,15 @@
         <v>145350</v>
       </c>
       <c r="Z8">
-        <f>T8*W8*0.6</f>
+        <f t="shared" si="1"/>
         <v>119850</v>
       </c>
       <c r="AA8">
+        <f t="shared" si="4"/>
+        <v>145350</v>
+      </c>
+      <c r="AC8">
         <f t="shared" si="2"/>
-        <v>145350</v>
-      </c>
-      <c r="AC8">
-        <f>V8*W8*0.6</f>
         <v>265200</v>
       </c>
       <c r="AE8">
@@ -7057,27 +7061,27 @@
         <v>6</v>
       </c>
       <c r="P9">
+        <f t="shared" si="5"/>
+        <v>1550</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="6"/>
+        <v>1850</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="7"/>
+        <v>2150</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="8"/>
+        <v>340000</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="9"/>
+        <v>400000</v>
+      </c>
+      <c r="V9">
         <f t="shared" si="3"/>
-        <v>1550</v>
-      </c>
-      <c r="Q9">
-        <f t="shared" si="4"/>
-        <v>1850</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="5"/>
-        <v>2150</v>
-      </c>
-      <c r="T9">
-        <f t="shared" si="6"/>
-        <v>340000</v>
-      </c>
-      <c r="U9">
-        <f t="shared" si="7"/>
-        <v>400000</v>
-      </c>
-      <c r="V9">
-        <f t="shared" si="1"/>
         <v>740000</v>
       </c>
       <c r="W9" s="29">
@@ -7090,15 +7094,15 @@
         <v>192000</v>
       </c>
       <c r="Z9">
-        <f>T9*W9*0.6</f>
+        <f t="shared" si="1"/>
         <v>163200</v>
       </c>
       <c r="AA9">
+        <f t="shared" si="4"/>
+        <v>192000</v>
+      </c>
+      <c r="AC9">
         <f t="shared" si="2"/>
-        <v>192000</v>
-      </c>
-      <c r="AC9">
-        <f>V9*W9*0.6</f>
         <v>355200</v>
       </c>
       <c r="AE9">
@@ -7152,27 +7156,27 @@
         <v>7</v>
       </c>
       <c r="P10">
+        <f t="shared" si="5"/>
+        <v>2150</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="6"/>
+        <v>2500</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="7"/>
+        <v>2850</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="8"/>
+        <v>465000</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="9"/>
+        <v>535000</v>
+      </c>
+      <c r="V10">
         <f t="shared" si="3"/>
-        <v>2150</v>
-      </c>
-      <c r="Q10">
-        <f t="shared" si="4"/>
-        <v>2500</v>
-      </c>
-      <c r="R10">
-        <f t="shared" si="5"/>
-        <v>2850</v>
-      </c>
-      <c r="T10">
-        <f t="shared" si="6"/>
-        <v>465000</v>
-      </c>
-      <c r="U10">
-        <f t="shared" si="7"/>
-        <v>535000</v>
-      </c>
-      <c r="V10">
-        <f t="shared" si="1"/>
         <v>1000000</v>
       </c>
       <c r="W10" s="30">
@@ -7185,15 +7189,15 @@
         <v>256800</v>
       </c>
       <c r="Z10">
-        <f>T10*W10*0.6</f>
+        <f t="shared" si="1"/>
         <v>223200</v>
       </c>
       <c r="AA10">
+        <f t="shared" si="4"/>
+        <v>256800</v>
+      </c>
+      <c r="AC10">
         <f t="shared" si="2"/>
-        <v>256800</v>
-      </c>
-      <c r="AC10">
-        <f>V10*W10*0.6</f>
         <v>480000</v>
       </c>
       <c r="AE10">
@@ -7247,27 +7251,27 @@
         <v>8</v>
       </c>
       <c r="P11">
+        <f t="shared" si="5"/>
+        <v>2850</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="6"/>
+        <v>3250</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="7"/>
+        <v>3650</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="8"/>
+        <v>610000</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="9"/>
+        <v>690000</v>
+      </c>
+      <c r="V11">
         <f t="shared" si="3"/>
-        <v>2850</v>
-      </c>
-      <c r="Q11">
-        <f t="shared" si="4"/>
-        <v>3250</v>
-      </c>
-      <c r="R11">
-        <f t="shared" si="5"/>
-        <v>3650</v>
-      </c>
-      <c r="T11">
-        <f t="shared" si="6"/>
-        <v>610000</v>
-      </c>
-      <c r="U11">
-        <f t="shared" si="7"/>
-        <v>690000</v>
-      </c>
-      <c r="V11">
-        <f t="shared" si="1"/>
         <v>1300000</v>
       </c>
       <c r="W11" s="30">
@@ -7280,15 +7284,15 @@
         <v>310500</v>
       </c>
       <c r="Z11">
-        <f>T11*W11*0.6</f>
+        <f t="shared" si="1"/>
         <v>274500</v>
       </c>
       <c r="AA11">
+        <f t="shared" si="4"/>
+        <v>310500</v>
+      </c>
+      <c r="AC11">
         <f t="shared" si="2"/>
-        <v>310500</v>
-      </c>
-      <c r="AC11">
-        <f>V11*W11*0.6</f>
         <v>585000</v>
       </c>
       <c r="AE11">
@@ -7342,27 +7346,27 @@
         <v>9</v>
       </c>
       <c r="P12">
+        <f t="shared" si="5"/>
+        <v>3650</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="6"/>
+        <v>4100</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="7"/>
+        <v>4550</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="8"/>
+        <v>775000</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="9"/>
+        <v>865000</v>
+      </c>
+      <c r="V12">
         <f t="shared" si="3"/>
-        <v>3650</v>
-      </c>
-      <c r="Q12">
-        <f t="shared" si="4"/>
-        <v>4100</v>
-      </c>
-      <c r="R12">
-        <f t="shared" si="5"/>
-        <v>4550</v>
-      </c>
-      <c r="T12">
-        <f t="shared" si="6"/>
-        <v>775000</v>
-      </c>
-      <c r="U12">
-        <f t="shared" si="7"/>
-        <v>865000</v>
-      </c>
-      <c r="V12">
-        <f t="shared" si="1"/>
         <v>1640000</v>
       </c>
       <c r="W12" s="29">
@@ -7375,15 +7379,15 @@
         <v>363300</v>
       </c>
       <c r="Z12">
-        <f>T12*W12*0.6</f>
+        <f t="shared" si="1"/>
         <v>325500</v>
       </c>
       <c r="AA12">
+        <f t="shared" si="4"/>
+        <v>363300</v>
+      </c>
+      <c r="AC12">
         <f t="shared" si="2"/>
-        <v>363300</v>
-      </c>
-      <c r="AC12">
-        <f>V12*W12*0.6</f>
         <v>688800</v>
       </c>
       <c r="AE12">
@@ -7437,27 +7441,27 @@
         <v>10</v>
       </c>
       <c r="P13">
+        <f t="shared" si="5"/>
+        <v>4550</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="6"/>
+        <v>5050</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="7"/>
+        <v>5550</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="8"/>
+        <v>960000</v>
+      </c>
+      <c r="U13">
+        <f t="shared" si="9"/>
+        <v>1060000</v>
+      </c>
+      <c r="V13">
         <f t="shared" si="3"/>
-        <v>4550</v>
-      </c>
-      <c r="Q13">
-        <f t="shared" si="4"/>
-        <v>5050</v>
-      </c>
-      <c r="R13">
-        <f t="shared" si="5"/>
-        <v>5550</v>
-      </c>
-      <c r="T13">
-        <f t="shared" si="6"/>
-        <v>960000</v>
-      </c>
-      <c r="U13">
-        <f t="shared" si="7"/>
-        <v>1060000</v>
-      </c>
-      <c r="V13">
-        <f t="shared" si="1"/>
         <v>2020000</v>
       </c>
       <c r="W13" s="29">
@@ -7470,15 +7474,15 @@
         <v>445200</v>
       </c>
       <c r="Z13">
-        <f>T13*W13*0.6</f>
+        <f t="shared" si="1"/>
         <v>403200</v>
       </c>
       <c r="AA13">
+        <f t="shared" si="4"/>
+        <v>445200</v>
+      </c>
+      <c r="AC13">
         <f t="shared" si="2"/>
-        <v>445200</v>
-      </c>
-      <c r="AC13">
-        <f>V13*W13*0.6</f>
         <v>848400</v>
       </c>
       <c r="AE13">
@@ -7532,27 +7536,27 @@
         <v>11</v>
       </c>
       <c r="P14">
+        <f t="shared" si="5"/>
+        <v>5550</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="6"/>
+        <v>6100</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="7"/>
+        <v>6650</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="8"/>
+        <v>1165000</v>
+      </c>
+      <c r="U14">
+        <f t="shared" si="9"/>
+        <v>1275000</v>
+      </c>
+      <c r="V14">
         <f t="shared" si="3"/>
-        <v>5550</v>
-      </c>
-      <c r="Q14">
-        <f t="shared" si="4"/>
-        <v>6100</v>
-      </c>
-      <c r="R14">
-        <f t="shared" si="5"/>
-        <v>6650</v>
-      </c>
-      <c r="T14">
-        <f t="shared" si="6"/>
-        <v>1165000</v>
-      </c>
-      <c r="U14">
-        <f t="shared" si="7"/>
-        <v>1275000</v>
-      </c>
-      <c r="V14">
-        <f t="shared" si="1"/>
         <v>2440000</v>
       </c>
       <c r="W14" s="30">
@@ -7565,15 +7569,15 @@
         <v>497250</v>
       </c>
       <c r="Z14">
-        <f>T14*W14*0.6</f>
+        <f t="shared" si="1"/>
         <v>454350</v>
       </c>
       <c r="AA14">
+        <f t="shared" si="4"/>
+        <v>497250</v>
+      </c>
+      <c r="AC14">
         <f t="shared" si="2"/>
-        <v>497250</v>
-      </c>
-      <c r="AC14">
-        <f>V14*W14*0.6</f>
         <v>951600</v>
       </c>
       <c r="AE14">
@@ -7627,27 +7631,27 @@
         <v>12</v>
       </c>
       <c r="P15">
+        <f t="shared" si="5"/>
+        <v>6650</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="6"/>
+        <v>7250</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="7"/>
+        <v>7850</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="8"/>
+        <v>1390000</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="9"/>
+        <v>1510000</v>
+      </c>
+      <c r="V15">
         <f t="shared" si="3"/>
-        <v>6650</v>
-      </c>
-      <c r="Q15">
-        <f t="shared" si="4"/>
-        <v>7250</v>
-      </c>
-      <c r="R15">
-        <f t="shared" si="5"/>
-        <v>7850</v>
-      </c>
-      <c r="T15">
-        <f t="shared" si="6"/>
-        <v>1390000</v>
-      </c>
-      <c r="U15">
-        <f t="shared" si="7"/>
-        <v>1510000</v>
-      </c>
-      <c r="V15">
-        <f t="shared" si="1"/>
         <v>2900000</v>
       </c>
       <c r="W15" s="30">
@@ -7660,15 +7664,15 @@
         <v>588900</v>
       </c>
       <c r="Z15">
-        <f>T15*W15*0.6</f>
+        <f t="shared" si="1"/>
         <v>542100</v>
       </c>
       <c r="AA15">
+        <f t="shared" si="4"/>
+        <v>588900</v>
+      </c>
+      <c r="AC15">
         <f t="shared" si="2"/>
-        <v>588900</v>
-      </c>
-      <c r="AC15">
-        <f>V15*W15*0.6</f>
         <v>1131000</v>
       </c>
       <c r="AE15">
@@ -7722,27 +7726,27 @@
         <v>13</v>
       </c>
       <c r="P16">
+        <f t="shared" si="5"/>
+        <v>7850</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="6"/>
+        <v>8500</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="7"/>
+        <v>9150</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="8"/>
+        <v>1635000</v>
+      </c>
+      <c r="U16">
+        <f t="shared" si="9"/>
+        <v>1765000</v>
+      </c>
+      <c r="V16">
         <f t="shared" si="3"/>
-        <v>7850</v>
-      </c>
-      <c r="Q16">
-        <f t="shared" si="4"/>
-        <v>8500</v>
-      </c>
-      <c r="R16">
-        <f t="shared" si="5"/>
-        <v>9150</v>
-      </c>
-      <c r="T16">
-        <f t="shared" si="6"/>
-        <v>1635000</v>
-      </c>
-      <c r="U16">
-        <f t="shared" si="7"/>
-        <v>1765000</v>
-      </c>
-      <c r="V16">
-        <f t="shared" si="1"/>
         <v>3400000</v>
       </c>
       <c r="W16" s="29">
@@ -7755,15 +7759,15 @@
         <v>635400</v>
       </c>
       <c r="Z16">
-        <f>T16*W16*0.6</f>
+        <f t="shared" si="1"/>
         <v>588600</v>
       </c>
       <c r="AA16">
+        <f t="shared" si="4"/>
+        <v>635400</v>
+      </c>
+      <c r="AC16">
         <f t="shared" si="2"/>
-        <v>635400</v>
-      </c>
-      <c r="AC16">
-        <f>V16*W16*0.6</f>
         <v>1224000</v>
       </c>
       <c r="AE16">
@@ -7817,27 +7821,27 @@
         <v>14</v>
       </c>
       <c r="P17">
+        <f t="shared" si="5"/>
+        <v>9150</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="6"/>
+        <v>9850</v>
+      </c>
+      <c r="R17">
+        <f t="shared" si="7"/>
+        <v>10550</v>
+      </c>
+      <c r="T17">
+        <f t="shared" si="8"/>
+        <v>1900000</v>
+      </c>
+      <c r="U17">
+        <f t="shared" si="9"/>
+        <v>2040000</v>
+      </c>
+      <c r="V17">
         <f t="shared" si="3"/>
-        <v>9150</v>
-      </c>
-      <c r="Q17">
-        <f t="shared" si="4"/>
-        <v>9850</v>
-      </c>
-      <c r="R17">
-        <f t="shared" si="5"/>
-        <v>10550</v>
-      </c>
-      <c r="T17">
-        <f t="shared" si="6"/>
-        <v>1900000</v>
-      </c>
-      <c r="U17">
-        <f t="shared" si="7"/>
-        <v>2040000</v>
-      </c>
-      <c r="V17">
-        <f t="shared" si="1"/>
         <v>3940000</v>
       </c>
       <c r="W17" s="29">
@@ -7850,15 +7854,15 @@
         <v>734400</v>
       </c>
       <c r="Z17">
-        <f>T17*W17*0.6</f>
+        <f t="shared" si="1"/>
         <v>684000</v>
       </c>
       <c r="AA17">
+        <f t="shared" si="4"/>
+        <v>734400</v>
+      </c>
+      <c r="AC17">
         <f t="shared" si="2"/>
-        <v>734400</v>
-      </c>
-      <c r="AC17">
-        <f>V17*W17*0.6</f>
         <v>1418400</v>
       </c>
       <c r="AE17">
@@ -7912,27 +7916,27 @@
         <v>15</v>
       </c>
       <c r="P18">
+        <f t="shared" si="5"/>
+        <v>10550</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" si="6"/>
+        <v>11300</v>
+      </c>
+      <c r="R18">
+        <f t="shared" si="7"/>
+        <v>12050</v>
+      </c>
+      <c r="T18">
+        <f t="shared" si="8"/>
+        <v>2185000</v>
+      </c>
+      <c r="U18">
+        <f t="shared" si="9"/>
+        <v>2335000</v>
+      </c>
+      <c r="V18">
         <f t="shared" si="3"/>
-        <v>10550</v>
-      </c>
-      <c r="Q18">
-        <f t="shared" si="4"/>
-        <v>11300</v>
-      </c>
-      <c r="R18">
-        <f t="shared" si="5"/>
-        <v>12050</v>
-      </c>
-      <c r="T18">
-        <f t="shared" si="6"/>
-        <v>2185000</v>
-      </c>
-      <c r="U18">
-        <f t="shared" si="7"/>
-        <v>2335000</v>
-      </c>
-      <c r="V18">
-        <f t="shared" si="1"/>
         <v>4520000</v>
       </c>
       <c r="W18" s="29">
@@ -7945,15 +7949,15 @@
         <v>840600</v>
       </c>
       <c r="Z18">
-        <f>T18*W18*0.6</f>
+        <f t="shared" si="1"/>
         <v>786600</v>
       </c>
       <c r="AA18">
+        <f t="shared" si="4"/>
+        <v>840600</v>
+      </c>
+      <c r="AC18">
         <f t="shared" si="2"/>
-        <v>840600</v>
-      </c>
-      <c r="AC18">
-        <f>V18*W18*0.6</f>
         <v>1627200</v>
       </c>
       <c r="AE18">
@@ -8007,27 +8011,27 @@
         <v>16</v>
       </c>
       <c r="P19">
+        <f t="shared" si="5"/>
+        <v>12050</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="6"/>
+        <v>12850</v>
+      </c>
+      <c r="R19">
+        <f t="shared" si="7"/>
+        <v>13650</v>
+      </c>
+      <c r="T19">
+        <f t="shared" si="8"/>
+        <v>2490000</v>
+      </c>
+      <c r="U19">
+        <f t="shared" si="9"/>
+        <v>2650000</v>
+      </c>
+      <c r="V19">
         <f t="shared" si="3"/>
-        <v>12050</v>
-      </c>
-      <c r="Q19">
-        <f t="shared" si="4"/>
-        <v>12850</v>
-      </c>
-      <c r="R19">
-        <f t="shared" si="5"/>
-        <v>13650</v>
-      </c>
-      <c r="T19">
-        <f t="shared" si="6"/>
-        <v>2490000</v>
-      </c>
-      <c r="U19">
-        <f t="shared" si="7"/>
-        <v>2650000</v>
-      </c>
-      <c r="V19">
-        <f t="shared" si="1"/>
         <v>5140000</v>
       </c>
       <c r="W19" s="29">
@@ -8040,15 +8044,15 @@
         <v>954000</v>
       </c>
       <c r="Z19">
-        <f>T19*W19*0.6</f>
+        <f t="shared" si="1"/>
         <v>896400</v>
       </c>
       <c r="AA19">
+        <f t="shared" si="4"/>
+        <v>954000</v>
+      </c>
+      <c r="AC19">
         <f t="shared" si="2"/>
-        <v>954000</v>
-      </c>
-      <c r="AC19">
-        <f>V19*W19*0.6</f>
         <v>1850400</v>
       </c>
       <c r="AE19">
@@ -8102,27 +8106,27 @@
         <v>17</v>
       </c>
       <c r="P20">
+        <f t="shared" si="5"/>
+        <v>13650</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="6"/>
+        <v>14500</v>
+      </c>
+      <c r="R20">
+        <f t="shared" si="7"/>
+        <v>15350</v>
+      </c>
+      <c r="T20">
+        <f t="shared" si="8"/>
+        <v>2815000</v>
+      </c>
+      <c r="U20">
+        <f t="shared" si="9"/>
+        <v>2985000</v>
+      </c>
+      <c r="V20">
         <f t="shared" si="3"/>
-        <v>13650</v>
-      </c>
-      <c r="Q20">
-        <f t="shared" si="4"/>
-        <v>14500</v>
-      </c>
-      <c r="R20">
-        <f t="shared" si="5"/>
-        <v>15350</v>
-      </c>
-      <c r="T20">
-        <f t="shared" si="6"/>
-        <v>2815000</v>
-      </c>
-      <c r="U20">
-        <f t="shared" si="7"/>
-        <v>2985000</v>
-      </c>
-      <c r="V20">
-        <f t="shared" si="1"/>
         <v>5800000</v>
       </c>
       <c r="W20" s="29">
@@ -8135,15 +8139,15 @@
         <v>1074600</v>
       </c>
       <c r="Z20">
-        <f>T20*W20*0.6</f>
+        <f t="shared" si="1"/>
         <v>1013400</v>
       </c>
       <c r="AA20">
+        <f t="shared" si="4"/>
+        <v>1074600</v>
+      </c>
+      <c r="AC20">
         <f t="shared" si="2"/>
-        <v>1074600</v>
-      </c>
-      <c r="AC20">
-        <f>V20*W20*0.6</f>
         <v>2088000</v>
       </c>
       <c r="AE20">
@@ -8197,27 +8201,27 @@
         <v>18</v>
       </c>
       <c r="P21">
+        <f t="shared" si="5"/>
+        <v>15350</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="6"/>
+        <v>16250</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="7"/>
+        <v>17150</v>
+      </c>
+      <c r="T21">
+        <f t="shared" si="8"/>
+        <v>3160000</v>
+      </c>
+      <c r="U21">
+        <f t="shared" si="9"/>
+        <v>3340000</v>
+      </c>
+      <c r="V21">
         <f t="shared" si="3"/>
-        <v>15350</v>
-      </c>
-      <c r="Q21">
-        <f t="shared" si="4"/>
-        <v>16250</v>
-      </c>
-      <c r="R21">
-        <f t="shared" si="5"/>
-        <v>17150</v>
-      </c>
-      <c r="T21">
-        <f t="shared" si="6"/>
-        <v>3160000</v>
-      </c>
-      <c r="U21">
-        <f t="shared" si="7"/>
-        <v>3340000</v>
-      </c>
-      <c r="V21">
-        <f t="shared" si="1"/>
         <v>6500000</v>
       </c>
       <c r="W21" s="30">
@@ -8230,15 +8234,15 @@
         <v>1002000</v>
       </c>
       <c r="Z21">
-        <f>T21*W21*0.6</f>
+        <f t="shared" si="1"/>
         <v>948000</v>
       </c>
       <c r="AA21">
+        <f t="shared" si="4"/>
+        <v>1002000</v>
+      </c>
+      <c r="AC21">
         <f t="shared" si="2"/>
-        <v>1002000</v>
-      </c>
-      <c r="AC21">
-        <f>V21*W21*0.6</f>
         <v>1950000</v>
       </c>
       <c r="AE21">
@@ -8292,27 +8296,27 @@
         <v>19</v>
       </c>
       <c r="P22">
+        <f t="shared" si="5"/>
+        <v>17150</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="6"/>
+        <v>18100</v>
+      </c>
+      <c r="R22">
+        <f t="shared" si="7"/>
+        <v>19050</v>
+      </c>
+      <c r="T22">
+        <f t="shared" si="8"/>
+        <v>3525000</v>
+      </c>
+      <c r="U22">
+        <f t="shared" si="9"/>
+        <v>3715000</v>
+      </c>
+      <c r="V22">
         <f t="shared" si="3"/>
-        <v>17150</v>
-      </c>
-      <c r="Q22">
-        <f t="shared" si="4"/>
-        <v>18100</v>
-      </c>
-      <c r="R22">
-        <f t="shared" si="5"/>
-        <v>19050</v>
-      </c>
-      <c r="T22">
-        <f t="shared" si="6"/>
-        <v>3525000</v>
-      </c>
-      <c r="U22">
-        <f t="shared" si="7"/>
-        <v>3715000</v>
-      </c>
-      <c r="V22">
-        <f t="shared" si="1"/>
         <v>7240000</v>
       </c>
       <c r="W22" s="30">
@@ -8325,15 +8329,15 @@
         <v>1114500</v>
       </c>
       <c r="Z22">
-        <f>T22*W22*0.6</f>
+        <f t="shared" si="1"/>
         <v>1057500</v>
       </c>
       <c r="AA22">
+        <f t="shared" si="4"/>
+        <v>1114500</v>
+      </c>
+      <c r="AC22">
         <f t="shared" si="2"/>
-        <v>1114500</v>
-      </c>
-      <c r="AC22">
-        <f>V22*W22*0.6</f>
         <v>2172000</v>
       </c>
       <c r="AE22">
@@ -8387,27 +8391,27 @@
         <v>20</v>
       </c>
       <c r="P23">
+        <f t="shared" si="5"/>
+        <v>19050</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" si="6"/>
+        <v>20050</v>
+      </c>
+      <c r="R23">
+        <f t="shared" si="7"/>
+        <v>21050</v>
+      </c>
+      <c r="T23">
+        <f t="shared" si="8"/>
+        <v>3910000</v>
+      </c>
+      <c r="U23">
+        <f t="shared" si="9"/>
+        <v>4110000</v>
+      </c>
+      <c r="V23">
         <f t="shared" si="3"/>
-        <v>19050</v>
-      </c>
-      <c r="Q23">
-        <f t="shared" si="4"/>
-        <v>20050</v>
-      </c>
-      <c r="R23">
-        <f t="shared" si="5"/>
-        <v>21050</v>
-      </c>
-      <c r="T23">
-        <f t="shared" si="6"/>
-        <v>3910000</v>
-      </c>
-      <c r="U23">
-        <f t="shared" si="7"/>
-        <v>4110000</v>
-      </c>
-      <c r="V23">
-        <f t="shared" si="1"/>
         <v>8020000</v>
       </c>
       <c r="W23" s="29">
@@ -8420,15 +8424,15 @@
         <v>1233000</v>
       </c>
       <c r="Z23">
-        <f>T23*W23*0.6</f>
+        <f t="shared" si="1"/>
         <v>1173000</v>
       </c>
       <c r="AA23">
+        <f t="shared" si="4"/>
+        <v>1233000</v>
+      </c>
+      <c r="AC23">
         <f t="shared" si="2"/>
-        <v>1233000</v>
-      </c>
-      <c r="AC23">
-        <f>V23*W23*0.6</f>
         <v>2406000</v>
       </c>
       <c r="AE23">
@@ -8464,27 +8468,27 @@
         <v>21</v>
       </c>
       <c r="P24">
-        <f t="shared" ref="P24:P41" si="8">R23</f>
+        <f t="shared" ref="P24:P41" si="10">R23</f>
         <v>21050</v>
       </c>
       <c r="Q24">
-        <f t="shared" ref="Q24:Q41" si="9">P24+(M24-L24)*O24</f>
+        <f t="shared" ref="Q24:Q41" si="11">P24+(M24-L24)*O24</f>
         <v>22100</v>
       </c>
       <c r="R24">
-        <f t="shared" ref="R24:R41" si="10">Q24+(N24-M24)*O24</f>
+        <f t="shared" ref="R24:R41" si="12">Q24+(N24-M24)*O24</f>
         <v>23150</v>
       </c>
       <c r="T24">
-        <f t="shared" ref="T24:T41" si="11">50*(P24+Q24)/2*4</f>
+        <f t="shared" ref="T24:T41" si="13">50*(P24+Q24)/2*4</f>
         <v>4315000</v>
       </c>
       <c r="U24">
-        <f t="shared" ref="U24:U41" si="12">50*(R24+Q24)/2*4</f>
+        <f t="shared" ref="U24:U41" si="14">50*(R24+Q24)/2*4</f>
         <v>4525000</v>
       </c>
       <c r="V24">
-        <f t="shared" ref="V24:V41" si="13">U24+T24</f>
+        <f t="shared" ref="V24:V41" si="15">U24+T24</f>
         <v>8840000</v>
       </c>
       <c r="W24" s="29">
@@ -8497,15 +8501,15 @@
         <v>4072500</v>
       </c>
       <c r="Z24">
-        <f>T24*W24*0.6</f>
+        <f t="shared" si="1"/>
         <v>3883500</v>
       </c>
       <c r="AA24">
-        <f>U24*W24*0.6</f>
+        <f t="shared" ref="AA24:AA38" si="16">U24*W24*0.6</f>
         <v>4072500</v>
       </c>
       <c r="AC24">
-        <f>V24*W24*0.6</f>
+        <f t="shared" si="2"/>
         <v>7956000</v>
       </c>
       <c r="AG24">
@@ -8535,27 +8539,27 @@
         <v>22</v>
       </c>
       <c r="P25">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>23150</v>
       </c>
       <c r="Q25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>24250</v>
       </c>
       <c r="R25">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>25350</v>
       </c>
       <c r="T25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>4740000</v>
       </c>
       <c r="U25">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>4960000</v>
       </c>
       <c r="V25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>9700000</v>
       </c>
       <c r="W25" s="29">
@@ -8568,15 +8572,15 @@
         <v>7440000</v>
       </c>
       <c r="Z25">
-        <f>T25*W25*0.6</f>
+        <f t="shared" si="1"/>
         <v>7110000</v>
       </c>
       <c r="AA25">
-        <f>U25*W25*0.6</f>
+        <f t="shared" si="16"/>
         <v>7440000</v>
       </c>
       <c r="AC25">
-        <f>V25*W25*0.6</f>
+        <f t="shared" si="2"/>
         <v>14550000</v>
       </c>
       <c r="AG25">
@@ -8606,27 +8610,27 @@
         <v>23</v>
       </c>
       <c r="P26">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>25350</v>
       </c>
       <c r="Q26">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>26500</v>
       </c>
       <c r="R26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>27650</v>
       </c>
       <c r="T26">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>5185000</v>
       </c>
       <c r="U26">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>5415000</v>
       </c>
       <c r="V26">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>10600000</v>
       </c>
       <c r="W26" s="29">
@@ -8639,15 +8643,15 @@
         <v>11371500</v>
       </c>
       <c r="Z26">
-        <f>T26*W26*0.6</f>
+        <f t="shared" si="1"/>
         <v>10888500</v>
       </c>
       <c r="AA26">
-        <f>U26*W26*0.6</f>
+        <f t="shared" si="16"/>
         <v>11371500</v>
       </c>
       <c r="AC26">
-        <f>V26*W26*0.6</f>
+        <f t="shared" si="2"/>
         <v>22260000</v>
       </c>
       <c r="AG26">
@@ -8677,27 +8681,27 @@
         <v>24</v>
       </c>
       <c r="P27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>27650</v>
       </c>
       <c r="Q27">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>28850</v>
       </c>
       <c r="R27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>30050</v>
       </c>
       <c r="T27">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>5650000</v>
       </c>
       <c r="U27">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>5890000</v>
       </c>
       <c r="V27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>11540000</v>
       </c>
       <c r="W27" s="29">
@@ -8710,15 +8714,15 @@
         <v>15903000</v>
       </c>
       <c r="Z27">
-        <f>T27*W27*0.6</f>
+        <f t="shared" si="1"/>
         <v>15255000</v>
       </c>
       <c r="AA27">
-        <f>U27*W27*0.6</f>
+        <f t="shared" si="16"/>
         <v>15903000</v>
       </c>
       <c r="AC27">
-        <f>V27*W27*0.6</f>
+        <f t="shared" si="2"/>
         <v>31158000</v>
       </c>
       <c r="AG27">
@@ -8748,30 +8752,30 @@
         <v>25</v>
       </c>
       <c r="P28">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>30050</v>
       </c>
       <c r="Q28">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>31300</v>
       </c>
       <c r="R28">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>32550</v>
       </c>
       <c r="S28">
         <v>185</v>
       </c>
       <c r="T28">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>6135000</v>
       </c>
       <c r="U28">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>6385000</v>
       </c>
       <c r="V28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>12520000</v>
       </c>
       <c r="W28" s="29">
@@ -8784,15 +8788,15 @@
         <v>21070500</v>
       </c>
       <c r="Z28">
-        <f>T28*W28*0.6</f>
+        <f t="shared" si="1"/>
         <v>20245500</v>
       </c>
       <c r="AA28">
-        <f>U28*W28*0.6</f>
+        <f t="shared" si="16"/>
         <v>21070500</v>
       </c>
       <c r="AC28">
-        <f>V28*W28*0.6</f>
+        <f t="shared" si="2"/>
         <v>41316000</v>
       </c>
       <c r="AG28">
@@ -8822,30 +8826,30 @@
         <v>26</v>
       </c>
       <c r="P29">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>32550</v>
       </c>
       <c r="Q29">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>33850</v>
       </c>
       <c r="R29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>35150</v>
       </c>
       <c r="S29">
         <v>150</v>
       </c>
       <c r="T29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>6640000</v>
       </c>
       <c r="U29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>6900000</v>
       </c>
       <c r="V29">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>13540000</v>
       </c>
       <c r="W29" s="29">
@@ -8858,15 +8862,15 @@
         <v>26910000</v>
       </c>
       <c r="Z29">
-        <f>T29*W29*0.6</f>
+        <f t="shared" si="1"/>
         <v>25896000</v>
       </c>
       <c r="AA29">
-        <f>U29*W29*0.6</f>
+        <f t="shared" si="16"/>
         <v>26910000</v>
       </c>
       <c r="AC29">
-        <f>V29*W29*0.6</f>
+        <f t="shared" si="2"/>
         <v>52806000</v>
       </c>
       <c r="AG29">
@@ -8896,31 +8900,31 @@
         <v>27</v>
       </c>
       <c r="P30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>35150</v>
       </c>
       <c r="Q30">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>36500</v>
       </c>
       <c r="R30">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>37850</v>
       </c>
       <c r="S30">
-        <f t="shared" ref="S30" si="14">S28-S29</f>
+        <f t="shared" ref="S30" si="17">S28-S29</f>
         <v>35</v>
       </c>
       <c r="T30">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>7165000</v>
       </c>
       <c r="U30">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>7435000</v>
       </c>
       <c r="V30">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>14600000</v>
       </c>
       <c r="W30" s="29">
@@ -8933,15 +8937,15 @@
         <v>33457500</v>
       </c>
       <c r="Z30">
-        <f>T30*W30*0.6</f>
+        <f t="shared" si="1"/>
         <v>32242500</v>
       </c>
       <c r="AA30">
-        <f>U30*W30*0.6</f>
+        <f t="shared" si="16"/>
         <v>33457500</v>
       </c>
       <c r="AC30">
-        <f>V30*W30*0.6</f>
+        <f t="shared" si="2"/>
         <v>65700000</v>
       </c>
       <c r="AG30">
@@ -8971,27 +8975,27 @@
         <v>28</v>
       </c>
       <c r="P31">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>37850</v>
       </c>
       <c r="Q31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>39250</v>
       </c>
       <c r="R31">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>40650</v>
       </c>
       <c r="T31">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>7710000</v>
       </c>
       <c r="U31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>7990000</v>
       </c>
       <c r="V31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>15700000</v>
       </c>
       <c r="W31" s="29">
@@ -9004,15 +9008,15 @@
         <v>40749000</v>
       </c>
       <c r="Z31">
-        <f>T31*W31*0.6</f>
+        <f t="shared" si="1"/>
         <v>39321000</v>
       </c>
       <c r="AA31">
-        <f>U31*W31*0.6</f>
+        <f t="shared" si="16"/>
         <v>40749000</v>
       </c>
       <c r="AC31">
-        <f>V31*W31*0.6</f>
+        <f t="shared" si="2"/>
         <v>80070000</v>
       </c>
       <c r="AG31">
@@ -9042,27 +9046,27 @@
         <v>29</v>
       </c>
       <c r="P32">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>40650</v>
       </c>
       <c r="Q32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>42100</v>
       </c>
       <c r="R32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>43550</v>
       </c>
       <c r="T32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>8275000</v>
       </c>
       <c r="U32">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>8565000</v>
       </c>
       <c r="V32">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>16840000</v>
       </c>
       <c r="W32" s="29">
@@ -9075,15 +9079,15 @@
         <v>48820500</v>
       </c>
       <c r="Z32">
-        <f>T32*W32*0.6</f>
+        <f t="shared" si="1"/>
         <v>47167500</v>
       </c>
       <c r="AA32">
-        <f>U32*W32*0.6</f>
+        <f t="shared" si="16"/>
         <v>48820500</v>
       </c>
       <c r="AC32">
-        <f>V32*W32*0.6</f>
+        <f t="shared" si="2"/>
         <v>95988000</v>
       </c>
       <c r="AG32">
@@ -9113,27 +9117,27 @@
         <v>30</v>
       </c>
       <c r="P33">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>43550</v>
       </c>
       <c r="Q33">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>45050</v>
       </c>
       <c r="R33">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>46550</v>
       </c>
       <c r="T33">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>8860000</v>
       </c>
       <c r="U33">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>9160000</v>
       </c>
       <c r="V33">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>18020000</v>
       </c>
       <c r="W33" s="29">
@@ -9146,15 +9150,15 @@
         <v>57708000</v>
       </c>
       <c r="Z33">
-        <f>T33*W33*0.6</f>
+        <f t="shared" si="1"/>
         <v>55818000</v>
       </c>
       <c r="AA33">
-        <f>U33*W33*0.6</f>
+        <f t="shared" si="16"/>
         <v>57708000</v>
       </c>
       <c r="AC33">
-        <f>V33*W33*0.6</f>
+        <f t="shared" si="2"/>
         <v>113526000</v>
       </c>
       <c r="AG33">
@@ -9184,27 +9188,27 @@
         <v>31</v>
       </c>
       <c r="P34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>46550</v>
       </c>
       <c r="Q34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>48100</v>
       </c>
       <c r="R34">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>49650</v>
       </c>
       <c r="T34">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>9465000</v>
       </c>
       <c r="U34">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>9775000</v>
       </c>
       <c r="V34">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>19240000</v>
       </c>
       <c r="W34" s="29">
@@ -9217,15 +9221,15 @@
         <v>67447500</v>
       </c>
       <c r="Z34">
-        <f>T34*W34*0.6</f>
+        <f t="shared" si="1"/>
         <v>65308500</v>
       </c>
       <c r="AA34">
-        <f>U34*W34*0.6</f>
+        <f t="shared" si="16"/>
         <v>67447500</v>
       </c>
       <c r="AC34">
-        <f>V34*W34*0.6</f>
+        <f t="shared" si="2"/>
         <v>132756000</v>
       </c>
       <c r="AG34">
@@ -9255,27 +9259,27 @@
         <v>32</v>
       </c>
       <c r="P35">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>49650</v>
       </c>
       <c r="Q35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>51250</v>
       </c>
       <c r="R35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>52850</v>
       </c>
       <c r="T35">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>10090000</v>
       </c>
       <c r="U35">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>10410000</v>
       </c>
       <c r="V35">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>20500000</v>
       </c>
       <c r="W35" s="29">
@@ -9288,15 +9292,15 @@
         <v>78075000</v>
       </c>
       <c r="Z35">
-        <f>T35*W35*0.6</f>
+        <f t="shared" si="1"/>
         <v>75675000</v>
       </c>
       <c r="AA35">
-        <f>U35*W35*0.6</f>
+        <f t="shared" si="16"/>
         <v>78075000</v>
       </c>
       <c r="AC35">
-        <f>V35*W35*0.6</f>
+        <f t="shared" si="2"/>
         <v>153750000</v>
       </c>
       <c r="AG35">
@@ -9326,27 +9330,27 @@
         <v>33</v>
       </c>
       <c r="P36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>52850</v>
       </c>
       <c r="Q36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>54500</v>
       </c>
       <c r="R36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>56150</v>
       </c>
       <c r="T36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>10735000</v>
       </c>
       <c r="U36">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>11065000</v>
       </c>
       <c r="V36">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>21800000</v>
       </c>
       <c r="W36" s="29">
@@ -9359,15 +9363,15 @@
         <v>89626500</v>
       </c>
       <c r="Z36">
-        <f>T36*W36*0.6</f>
+        <f t="shared" si="1"/>
         <v>86953500</v>
       </c>
       <c r="AA36">
-        <f>U36*W36*0.6</f>
+        <f t="shared" si="16"/>
         <v>89626500</v>
       </c>
       <c r="AC36">
-        <f>V36*W36*0.6</f>
+        <f t="shared" si="2"/>
         <v>176580000</v>
       </c>
       <c r="AG36">
@@ -9397,27 +9401,27 @@
         <v>34</v>
       </c>
       <c r="P37">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>56150</v>
       </c>
       <c r="Q37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>57850</v>
       </c>
       <c r="R37">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>59550</v>
       </c>
       <c r="T37">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>11400000</v>
       </c>
       <c r="U37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>11740000</v>
       </c>
       <c r="V37">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>23140000</v>
       </c>
       <c r="W37" s="29">
@@ -9430,15 +9434,15 @@
         <v>102138000</v>
       </c>
       <c r="Z37">
-        <f>T37*W37*0.6</f>
+        <f t="shared" si="1"/>
         <v>99180000</v>
       </c>
       <c r="AA37">
-        <f>U37*W37*0.6</f>
+        <f t="shared" si="16"/>
         <v>102138000</v>
       </c>
       <c r="AC37">
-        <f>V37*W37*0.6</f>
+        <f t="shared" si="2"/>
         <v>201318000</v>
       </c>
       <c r="AG37">
@@ -9468,27 +9472,27 @@
         <v>35</v>
       </c>
       <c r="P38">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>59550</v>
       </c>
       <c r="Q38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>61300</v>
       </c>
       <c r="R38">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>63050</v>
       </c>
       <c r="T38">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>12085000</v>
       </c>
       <c r="U38">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>12435000</v>
       </c>
       <c r="V38">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>24520000</v>
       </c>
       <c r="W38" s="29">
@@ -9501,15 +9505,15 @@
         <v>115645500</v>
       </c>
       <c r="Z38">
-        <f>T38*W38*0.6</f>
+        <f t="shared" si="1"/>
         <v>112390500</v>
       </c>
       <c r="AA38">
-        <f>U38*W38*0.6</f>
+        <f t="shared" si="16"/>
         <v>115645500</v>
       </c>
       <c r="AC38">
-        <f>V38*W38*0.6</f>
+        <f t="shared" si="2"/>
         <v>228036000</v>
       </c>
       <c r="AG38">
@@ -9539,27 +9543,27 @@
         <v>36</v>
       </c>
       <c r="P39">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>63050</v>
       </c>
       <c r="Q39">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>64850</v>
       </c>
       <c r="R39">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>66650</v>
       </c>
       <c r="T39">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>12790000</v>
       </c>
       <c r="U39">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>13150000</v>
       </c>
       <c r="V39">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>25940000</v>
       </c>
       <c r="W39" s="29">
@@ -9576,11 +9580,11 @@
         <v>130185000</v>
       </c>
       <c r="AA39">
-        <f t="shared" ref="Y39:AA41" si="15">U39*W39*0.6</f>
+        <f t="shared" ref="AA39:AA41" si="18">U39*W39*0.6</f>
         <v>130185000</v>
       </c>
       <c r="AB39">
-        <f t="shared" ref="AB39:AB41" si="16">V39*W39*0.6</f>
+        <f t="shared" ref="AB39:AB41" si="19">V39*W39*0.6</f>
         <v>256806000</v>
       </c>
       <c r="AF39">
@@ -9610,27 +9614,27 @@
         <v>37</v>
       </c>
       <c r="P40">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>66650</v>
       </c>
       <c r="Q40">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>68500</v>
       </c>
       <c r="R40">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>70350</v>
       </c>
       <c r="T40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>13515000</v>
       </c>
       <c r="U40">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>13885000</v>
       </c>
       <c r="V40">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>27400000</v>
       </c>
       <c r="W40" s="29">
@@ -9647,11 +9651,11 @@
         <v>145792500</v>
       </c>
       <c r="AA40">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>145792500</v>
       </c>
       <c r="AB40">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>287700000</v>
       </c>
       <c r="AF40">
@@ -9681,27 +9685,27 @@
         <v>38</v>
       </c>
       <c r="P41">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>70350</v>
       </c>
       <c r="Q41">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>72250</v>
       </c>
       <c r="R41">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>74150</v>
       </c>
       <c r="T41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>14260000</v>
       </c>
       <c r="U41">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>14640000</v>
       </c>
       <c r="V41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>28900000</v>
       </c>
       <c r="W41" s="29">
@@ -9718,11 +9722,11 @@
         <v>162504000</v>
       </c>
       <c r="AA41">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>162504000</v>
       </c>
       <c r="AB41">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>320790000</v>
       </c>
       <c r="AF41">
@@ -10411,28 +10415,82 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA2454FF-C9F1-41C0-86BA-697477BDDF4E}">
-  <dimension ref="B1:AK103"/>
+  <dimension ref="A1:AK103"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="3" max="3" width="12.375" customWidth="1"/>
     <col min="8" max="8" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" customWidth="1"/>
     <col min="10" max="10" width="18.875" customWidth="1"/>
+    <col min="11" max="11" width="12.125" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="13.125" bestFit="1" customWidth="1"/>
     <col min="18" max="19" width="13.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="N1" s="38" t="s">
+    <row r="1" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" s="7"/>
+      <c r="J1" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="N1" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
-      <c r="R1" s="38"/>
-      <c r="S1" s="38"/>
-      <c r="T1" s="38"/>
-    </row>
-    <row r="2" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="10">
+        <v>1000000000</v>
+      </c>
+      <c r="D2" s="10">
+        <v>1</v>
+      </c>
+      <c r="E2" s="10">
+        <v>113608</v>
+      </c>
+      <c r="F2" s="10">
+        <v>0</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="11"/>
       <c r="O2" s="6" t="s">
         <v>21</v>
       </c>
@@ -10452,7 +10510,31 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="10">
+        <v>1000000000</v>
+      </c>
+      <c r="D3" s="10">
+        <v>1</v>
+      </c>
+      <c r="E3" s="10">
+        <v>113608</v>
+      </c>
+      <c r="F3" s="10">
+        <v>0</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="11"/>
       <c r="N3" t="s">
         <v>23</v>
       </c>
@@ -10480,7 +10562,38 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="10">
+        <v>1500000000</v>
+      </c>
+      <c r="D4" s="10">
+        <v>1</v>
+      </c>
+      <c r="E4" s="10">
+        <v>250501608</v>
+      </c>
+      <c r="F4" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="10">
+        <f>1000/2*(C4+999*E4)</f>
+        <v>125875553196000</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="O4" s="9" t="s">
         <v>0</v>
       </c>
@@ -10508,7 +10621,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="3:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="10">
+        <v>1500000000</v>
+      </c>
+      <c r="D5" s="10">
+        <v>1</v>
+      </c>
+      <c r="E5" s="10">
+        <v>21501608</v>
+      </c>
+      <c r="F5" s="10">
+        <v>5000</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="10">
+        <f>5000/2*(C5+5000*E5)</f>
+        <v>272520100000000</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>31</v>
+      </c>
       <c r="O5" s="9" t="s">
         <v>32</v>
       </c>
@@ -10528,7 +10672,38 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6">
+        <v>251751106392</v>
+      </c>
+      <c r="D6" s="10">
+        <v>100</v>
+      </c>
+      <c r="E6">
+        <v>800000000</v>
+      </c>
+      <c r="F6" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="10">
+        <f>1000/2*(C6+999*E6)</f>
+        <v>525475553196000</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>41</v>
+      </c>
       <c r="N6" t="s">
         <v>42</v>
       </c>
@@ -10551,7 +10726,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7">
+        <v>108986538392</v>
+      </c>
+      <c r="D7" s="10">
+        <v>100</v>
+      </c>
+      <c r="E7">
+        <v>420000000</v>
+      </c>
+      <c r="F7" s="10">
+        <v>5000</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="10">
+        <f>5000/2*(C7+5000*E7)</f>
+        <v>5522466345980000</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>46</v>
+      </c>
       <c r="O7" s="9">
         <v>5000</v>
       </c>
@@ -10579,7 +10785,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="14"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="16"/>
       <c r="O8" s="9" t="s">
         <v>0</v>
       </c>
@@ -10604,7 +10820,7 @@
         <v>109008040000</v>
       </c>
     </row>
-    <row r="9" spans="3:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C9" t="s">
         <v>0</v>
       </c>
@@ -10627,18 +10843,18 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="3:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="N11" s="38" t="s">
+    <row r="11" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N11" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="O11" s="38"/>
-      <c r="P11" s="38"/>
-      <c r="Q11" s="38"/>
-      <c r="R11" s="38"/>
-      <c r="S11" s="38"/>
-      <c r="T11" s="38"/>
-    </row>
-    <row r="12" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="O11" s="39"/>
+      <c r="P11" s="39"/>
+      <c r="Q11" s="39"/>
+      <c r="R11" s="39"/>
+      <c r="S11" s="39"/>
+      <c r="T11" s="39"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="N12" t="s">
         <v>23</v>
       </c>
@@ -10661,11 +10877,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="G13" s="38" t="s">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="G13" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="H13" s="38"/>
+      <c r="H13" s="39"/>
       <c r="I13">
         <v>1000</v>
       </c>
@@ -10693,11 +10909,11 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="14" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="G14" s="38" t="s">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="G14" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="H14" s="38"/>
+      <c r="H14" s="39"/>
       <c r="I14">
         <f>D72+I$13*F72</f>
         <v>252001608000</v>
@@ -10727,11 +10943,11 @@
         <v>1051751106392</v>
       </c>
     </row>
-    <row r="15" spans="3:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G15" s="38" t="s">
+    <row r="15" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G15" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="H15" s="38"/>
+      <c r="H15" s="39"/>
       <c r="I15">
         <f>D72+I$13*F73</f>
         <v>23001608000</v>
@@ -10758,7 +10974,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="3:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N16" t="s">
         <v>42</v>
       </c>
@@ -10788,6 +11004,9 @@
       <c r="D17" s="8">
         <v>1000000</v>
       </c>
+      <c r="I17">
+        <v>5000</v>
+      </c>
       <c r="O17" s="9">
         <v>5000</v>
       </c>
@@ -10819,17 +11038,8 @@
       <c r="D18" s="11">
         <v>10000000</v>
       </c>
-      <c r="G18" t="s">
-        <v>61</v>
-      </c>
       <c r="H18" t="s">
-        <v>62</v>
-      </c>
-      <c r="I18">
-        <v>1000</v>
-      </c>
-      <c r="K18" s="17">
-        <v>0.5</v>
+        <v>131</v>
       </c>
       <c r="O18" s="9"/>
       <c r="P18" s="10">
@@ -10860,17 +11070,13 @@
       <c r="D19" s="11">
         <v>100000000</v>
       </c>
-      <c r="G19" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="H19" s="38"/>
+      <c r="G19" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="H19" s="39"/>
       <c r="I19">
-        <f>I$18/2*((2*D72)+(I$18-1)*F72)</f>
-        <v>126625553196000</v>
-      </c>
-      <c r="K19">
-        <f>I19/2</f>
-        <v>63312776598000</v>
+        <f>C4+(1000)*E4</f>
+        <v>252001608000</v>
       </c>
       <c r="O19" s="14" t="s">
         <v>32</v>
@@ -10898,17 +11104,13 @@
       <c r="D20" s="11">
         <v>1000000000</v>
       </c>
-      <c r="G20" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="H20" s="38"/>
+      <c r="G20" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="H20" s="39"/>
       <c r="I20">
-        <f>I$18/2*((2*D73)+(I$18-1)*F73)</f>
-        <v>12240053196000</v>
-      </c>
-      <c r="K20">
-        <f>I20/2</f>
-        <v>6120026598000</v>
+        <f>C5+(5000)*E5</f>
+        <v>109008040000</v>
       </c>
     </row>
     <row r="21" spans="3:37" x14ac:dyDescent="0.3">
@@ -10937,6 +11139,18 @@
       <c r="D23" s="11">
         <v>1000000000000</v>
       </c>
+      <c r="G23" t="s">
+        <v>61</v>
+      </c>
+      <c r="H23" t="s">
+        <v>62</v>
+      </c>
+      <c r="I23">
+        <v>1000</v>
+      </c>
+      <c r="K23" s="17">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="24" spans="3:37" x14ac:dyDescent="0.3">
       <c r="C24" s="9" t="s">
@@ -10945,6 +11159,22 @@
       <c r="D24" s="11">
         <v>10000000000000</v>
       </c>
+      <c r="G24" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="H24" s="39"/>
+      <c r="I24">
+        <f>I$23/2*((2*C6)+(I$23-1)*E6)</f>
+        <v>651351106392000</v>
+      </c>
+      <c r="J24">
+        <f>I24/I24</f>
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <f>I24*0.4</f>
+        <v>260540442556800</v>
+      </c>
     </row>
     <row r="25" spans="3:37" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C25" s="14" t="s">
@@ -10952,6 +11182,22 @@
       </c>
       <c r="D25" s="16">
         <v>100000000000000</v>
+      </c>
+      <c r="G25" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="H25" s="39"/>
+      <c r="I25">
+        <f>I17/2*((2*C7)+(I17-1)*E7)</f>
+        <v>5793882691960000</v>
+      </c>
+      <c r="J25">
+        <f>I25/I24</f>
+        <v>8.8951759429008952</v>
+      </c>
+      <c r="K25">
+        <f>I25*0.4</f>
+        <v>2317553076784000</v>
       </c>
       <c r="Z25">
         <v>1000000000</v>
@@ -11206,19 +11452,19 @@
       </c>
     </row>
     <row r="53" spans="4:21" x14ac:dyDescent="0.3">
-      <c r="F53" s="39" t="s">
+      <c r="F53" s="38" t="s">
         <v>121</v>
       </c>
-      <c r="G53" s="39"/>
-      <c r="H53" s="39"/>
-      <c r="I53" s="39"/>
-      <c r="M53" s="39" t="s">
+      <c r="G53" s="38"/>
+      <c r="H53" s="38"/>
+      <c r="I53" s="38"/>
+      <c r="M53" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="N53" s="39"/>
-      <c r="O53" s="39"/>
-      <c r="P53" s="39"/>
-      <c r="Q53" s="39"/>
+      <c r="N53" s="38"/>
+      <c r="O53" s="38"/>
+      <c r="P53" s="38"/>
+      <c r="Q53" s="38"/>
     </row>
     <row r="55" spans="4:21" x14ac:dyDescent="0.3">
       <c r="I55" s="37">
@@ -11359,7 +11605,7 @@
         <v>788069056170</v>
       </c>
       <c r="T58" s="36">
-        <f t="shared" ref="T58:U76" si="10">S58/(10^9)</f>
+        <f t="shared" ref="T58:T76" si="10">S58/(10^9)</f>
         <v>788.06905616999995</v>
       </c>
     </row>
@@ -12401,24 +12647,27 @@
       </c>
     </row>
     <row r="80" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="F80" s="39" t="s">
+      <c r="F80" s="38" t="s">
         <v>128</v>
       </c>
-      <c r="G80" s="39"/>
-      <c r="H80" s="39"/>
-      <c r="I80" s="39"/>
-      <c r="M80" s="39" t="s">
+      <c r="G80" s="38"/>
+      <c r="H80" s="38"/>
+      <c r="I80" s="38"/>
+      <c r="M80" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="N80" s="39"/>
-      <c r="O80" s="39"/>
-      <c r="P80" s="39"/>
-      <c r="Q80" s="39"/>
+      <c r="N80" s="38"/>
+      <c r="O80" s="38"/>
+      <c r="P80" s="38"/>
+      <c r="Q80" s="38"/>
     </row>
     <row r="82" spans="4:22" x14ac:dyDescent="0.3">
       <c r="I82" s="37">
         <v>60</v>
       </c>
+      <c r="K82">
+        <v>9</v>
+      </c>
       <c r="Q82" s="35">
         <v>60</v>
       </c>
@@ -12452,23 +12701,23 @@
         <v>0.1</v>
       </c>
       <c r="F84">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H84" s="32">
         <f>F84/2*((2*D$74)+(F84-1)*F$74)</f>
-        <v>29135110639200</v>
+        <v>13567555319600</v>
       </c>
       <c r="I84" s="33">
-        <f>INT(H84*(1-I$82/100))</f>
-        <v>11654044255680</v>
+        <f>H84*0.4</f>
+        <v>5427022127840</v>
       </c>
       <c r="J84">
-        <f>I84*0.6</f>
-        <v>6992426553408</v>
+        <f>I84*1</f>
+        <v>5427022127840</v>
       </c>
       <c r="K84" s="36">
-        <f>J84/(10^10)</f>
-        <v>699.24265534079996</v>
+        <f>J84/(10^9)</f>
+        <v>5427.0221278400004</v>
       </c>
       <c r="M84">
         <v>5000</v>
@@ -12485,7 +12734,7 @@
         <v>40319134598000</v>
       </c>
       <c r="R84" s="33">
-        <f>INT(Q84*(1-Q$82/100))</f>
+        <f t="shared" ref="R84:R87" si="12">Q84*0.4</f>
         <v>16127653839200</v>
       </c>
       <c r="S84">
@@ -12508,27 +12757,26 @@
         <v>0.2</v>
       </c>
       <c r="F85">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G85">
-        <f t="shared" ref="G85:G93" si="12">F84</f>
         <v>100</v>
       </c>
       <c r="H85" s="32">
         <f>F85/2*((2*D$74)+(F85-1)*F$74)-G85/2*((2*D$74)+(G85-1)*F$74)</f>
-        <v>37135110639200</v>
+        <v>17567555319600</v>
       </c>
       <c r="I85" s="33">
-        <f t="shared" ref="I85:I93" si="13">INT(H85*(1-I$82/100))</f>
-        <v>14854044255680</v>
+        <f t="shared" ref="I85:I93" si="13">H85*0.4</f>
+        <v>7027022127840</v>
       </c>
       <c r="J85">
-        <f t="shared" ref="J85:J93" si="14">I85*0.6</f>
-        <v>8912426553408</v>
+        <f t="shared" ref="J85:J93" si="14">I85*1</f>
+        <v>7027022127840</v>
       </c>
       <c r="K85" s="36">
-        <f t="shared" ref="K85:K93" si="15">J85/(10^10)</f>
-        <v>891.24265534079996</v>
+        <f t="shared" ref="K85:K93" si="15">J85/(10^9)</f>
+        <v>7027.0221278400004</v>
       </c>
       <c r="M85">
         <v>5000</v>
@@ -12549,15 +12797,15 @@
         <v>66569134598000</v>
       </c>
       <c r="R85" s="33">
-        <f t="shared" ref="R85:R103" si="17">INT(Q85*(1-Q$82/100))</f>
+        <f t="shared" si="12"/>
         <v>26627653839200</v>
       </c>
       <c r="S85">
-        <f t="shared" ref="S85:S103" si="18">R85*1</f>
+        <f t="shared" ref="S85:S103" si="17">R85*1</f>
         <v>26627653839200</v>
       </c>
       <c r="T85" s="36">
-        <f t="shared" ref="T85:T103" si="19">S85/(10^10)</f>
+        <f t="shared" ref="T85:T103" si="18">S85/(10^10)</f>
         <v>2662.7653839200002</v>
       </c>
       <c r="V85">
@@ -12572,27 +12820,26 @@
         <v>0.3</v>
       </c>
       <c r="F86">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G86">
-        <f t="shared" si="12"/>
         <v>200</v>
       </c>
       <c r="H86" s="32">
-        <f t="shared" ref="H86:H93" si="20">F86/2*((2*D$74)+(F86-1)*F$74)-G86/2*((2*D$74)+(G86-1)*F$74)</f>
-        <v>45135110639200</v>
+        <f t="shared" ref="H86:H93" si="19">F86/2*((2*D$74)+(F86-1)*F$74)-G86/2*((2*D$74)+(G86-1)*F$74)</f>
+        <v>21567555319600</v>
       </c>
       <c r="I86" s="33">
         <f t="shared" si="13"/>
-        <v>18054044255680</v>
+        <v>8627022127840</v>
       </c>
       <c r="J86">
         <f t="shared" si="14"/>
-        <v>10832426553408</v>
+        <v>8627022127840</v>
       </c>
       <c r="K86" s="36">
         <f t="shared" si="15"/>
-        <v>1083.2426553408</v>
+        <v>8627.0221278400004</v>
       </c>
       <c r="M86">
         <v>5000</v>
@@ -12605,23 +12852,23 @@
         <v>750</v>
       </c>
       <c r="P86">
-        <f t="shared" ref="P86:P103" si="21">O85</f>
+        <f t="shared" ref="P86:P103" si="20">O85</f>
         <v>500</v>
       </c>
       <c r="Q86" s="32">
-        <f t="shared" ref="Q86:Q103" si="22">O86/2*((2*D$75)+(O86-1)*F$75)-P86/2*((2*D$75)+(P86-1)*F$75)</f>
+        <f t="shared" ref="Q86:Q103" si="21">O86/2*((2*D$75)+(O86-1)*F$75)-P86/2*((2*D$75)+(P86-1)*F$75)</f>
         <v>92819134598000</v>
       </c>
       <c r="R86" s="33">
+        <f t="shared" si="12"/>
+        <v>37127653839200</v>
+      </c>
+      <c r="S86">
         <f t="shared" si="17"/>
         <v>37127653839200</v>
       </c>
-      <c r="S86">
+      <c r="T86" s="36">
         <f t="shared" si="18"/>
-        <v>37127653839200</v>
-      </c>
-      <c r="T86" s="36">
-        <f t="shared" si="19"/>
         <v>3712.7653839200002</v>
       </c>
       <c r="V86">
@@ -12636,27 +12883,26 @@
         <v>0.4</v>
       </c>
       <c r="F87">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="G87">
-        <f t="shared" si="12"/>
         <v>300</v>
       </c>
       <c r="H87" s="32">
-        <f t="shared" si="20"/>
-        <v>53135110639200</v>
+        <f t="shared" si="19"/>
+        <v>25567555319600</v>
       </c>
       <c r="I87" s="33">
         <f t="shared" si="13"/>
-        <v>21254044255680</v>
+        <v>10227022127840</v>
       </c>
       <c r="J87">
         <f t="shared" si="14"/>
-        <v>12752426553408</v>
+        <v>10227022127840</v>
       </c>
       <c r="K87" s="36">
         <f t="shared" si="15"/>
-        <v>1275.2426553408</v>
+        <v>10227.02212784</v>
       </c>
       <c r="M87">
         <v>5000</v>
@@ -12669,23 +12915,23 @@
         <v>1000</v>
       </c>
       <c r="P87">
+        <f t="shared" si="20"/>
+        <v>750</v>
+      </c>
+      <c r="Q87" s="32">
         <f t="shared" si="21"/>
-        <v>750</v>
-      </c>
-      <c r="Q87" s="32">
-        <f t="shared" si="22"/>
         <v>119069134598000</v>
       </c>
       <c r="R87" s="33">
+        <f t="shared" si="12"/>
+        <v>47627653839200</v>
+      </c>
+      <c r="S87">
         <f t="shared" si="17"/>
         <v>47627653839200</v>
       </c>
-      <c r="S87">
+      <c r="T87" s="36">
         <f t="shared" si="18"/>
-        <v>47627653839200</v>
-      </c>
-      <c r="T87" s="36">
-        <f t="shared" si="19"/>
         <v>4762.7653839200002</v>
       </c>
       <c r="U87" t="s">
@@ -12703,27 +12949,26 @@
         <v>0.5</v>
       </c>
       <c r="F88">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="G88">
-        <f t="shared" si="12"/>
         <v>400</v>
       </c>
       <c r="H88" s="32">
-        <f t="shared" si="20"/>
-        <v>61135110639200</v>
+        <f t="shared" si="19"/>
+        <v>29567555319600</v>
       </c>
       <c r="I88" s="33">
         <f t="shared" si="13"/>
-        <v>24454044255680</v>
+        <v>11827022127840</v>
       </c>
       <c r="J88">
         <f t="shared" si="14"/>
-        <v>14672426553408</v>
+        <v>11827022127840</v>
       </c>
       <c r="K88" s="36">
         <f t="shared" si="15"/>
-        <v>1467.2426553408</v>
+        <v>11827.02212784</v>
       </c>
       <c r="M88">
         <v>5000</v>
@@ -12736,23 +12981,23 @@
         <v>1250</v>
       </c>
       <c r="P88">
+        <f t="shared" si="20"/>
+        <v>1000</v>
+      </c>
+      <c r="Q88" s="32">
         <f t="shared" si="21"/>
-        <v>1000</v>
-      </c>
-      <c r="Q88" s="32">
-        <f t="shared" si="22"/>
         <v>145319134598000</v>
       </c>
       <c r="R88" s="33">
+        <f>Q88*0.4</f>
+        <v>58127653839200</v>
+      </c>
+      <c r="S88">
         <f t="shared" si="17"/>
         <v>58127653839200</v>
       </c>
-      <c r="S88">
+      <c r="T88" s="36">
         <f t="shared" si="18"/>
-        <v>58127653839200</v>
-      </c>
-      <c r="T88" s="36">
-        <f t="shared" si="19"/>
         <v>5812.7653839200002</v>
       </c>
       <c r="V88">
@@ -12767,27 +13012,26 @@
         <v>0.6</v>
       </c>
       <c r="F89">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="G89">
-        <f t="shared" si="12"/>
         <v>500</v>
       </c>
       <c r="H89" s="32">
-        <f t="shared" si="20"/>
-        <v>69135110639200</v>
+        <f t="shared" si="19"/>
+        <v>33567555319600</v>
       </c>
       <c r="I89" s="33">
         <f t="shared" si="13"/>
-        <v>27654044255680</v>
+        <v>13427022127840</v>
       </c>
       <c r="J89">
         <f t="shared" si="14"/>
-        <v>16592426553408</v>
+        <v>13427022127840</v>
       </c>
       <c r="K89" s="36">
         <f t="shared" si="15"/>
-        <v>1659.2426553408</v>
+        <v>13427.02212784</v>
       </c>
       <c r="M89">
         <v>5000</v>
@@ -12800,23 +13044,23 @@
         <v>1500</v>
       </c>
       <c r="P89">
+        <f t="shared" si="20"/>
+        <v>1250</v>
+      </c>
+      <c r="Q89" s="32">
         <f t="shared" si="21"/>
-        <v>1250</v>
-      </c>
-      <c r="Q89" s="32">
-        <f t="shared" si="22"/>
         <v>171569134598000</v>
       </c>
       <c r="R89" s="33">
+        <f t="shared" ref="R89:R103" si="22">Q89*0.4</f>
+        <v>68627653839200</v>
+      </c>
+      <c r="S89">
         <f t="shared" si="17"/>
         <v>68627653839200</v>
       </c>
-      <c r="S89">
+      <c r="T89" s="36">
         <f t="shared" si="18"/>
-        <v>68627653839200</v>
-      </c>
-      <c r="T89" s="36">
-        <f t="shared" si="19"/>
         <v>6862.7653839200002</v>
       </c>
       <c r="V89">
@@ -12831,27 +13075,26 @@
         <v>0.7</v>
       </c>
       <c r="F90">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="G90">
-        <f t="shared" si="12"/>
         <v>600</v>
       </c>
       <c r="H90" s="32">
-        <f t="shared" si="20"/>
-        <v>77135110639200</v>
+        <f t="shared" si="19"/>
+        <v>37567555319600</v>
       </c>
       <c r="I90" s="33">
         <f t="shared" si="13"/>
-        <v>30854044255680</v>
+        <v>15027022127840</v>
       </c>
       <c r="J90">
         <f t="shared" si="14"/>
-        <v>18512426553408</v>
+        <v>15027022127840</v>
       </c>
       <c r="K90" s="36">
         <f t="shared" si="15"/>
-        <v>1851.2426553408</v>
+        <v>15027.02212784</v>
       </c>
       <c r="M90">
         <v>5000</v>
@@ -12864,23 +13107,23 @@
         <v>1750</v>
       </c>
       <c r="P90">
+        <f t="shared" si="20"/>
+        <v>1500</v>
+      </c>
+      <c r="Q90" s="32">
         <f t="shared" si="21"/>
-        <v>1500</v>
-      </c>
-      <c r="Q90" s="32">
+        <v>197819134598000</v>
+      </c>
+      <c r="R90" s="33">
         <f t="shared" si="22"/>
-        <v>197819134598000</v>
-      </c>
-      <c r="R90" s="33">
+        <v>79127653839200</v>
+      </c>
+      <c r="S90">
         <f t="shared" si="17"/>
         <v>79127653839200</v>
       </c>
-      <c r="S90">
+      <c r="T90" s="36">
         <f t="shared" si="18"/>
-        <v>79127653839200</v>
-      </c>
-      <c r="T90" s="36">
-        <f t="shared" si="19"/>
         <v>7912.7653839200002</v>
       </c>
       <c r="V90">
@@ -12895,27 +13138,26 @@
         <v>0.8</v>
       </c>
       <c r="F91">
-        <v>800</v>
+        <v>750</v>
       </c>
       <c r="G91">
-        <f t="shared" si="12"/>
         <v>700</v>
       </c>
       <c r="H91" s="32">
-        <f t="shared" si="20"/>
-        <v>85135110639200</v>
+        <f t="shared" si="19"/>
+        <v>41567555319600</v>
       </c>
       <c r="I91" s="33">
         <f t="shared" si="13"/>
-        <v>34054044255680</v>
+        <v>16627022127840</v>
       </c>
       <c r="J91">
         <f t="shared" si="14"/>
-        <v>20432426553408</v>
+        <v>16627022127840</v>
       </c>
       <c r="K91" s="36">
         <f t="shared" si="15"/>
-        <v>2043.2426553408</v>
+        <v>16627.022127839999</v>
       </c>
       <c r="M91">
         <v>5000</v>
@@ -12928,23 +13170,23 @@
         <v>2000</v>
       </c>
       <c r="P91">
+        <f t="shared" si="20"/>
+        <v>1750</v>
+      </c>
+      <c r="Q91" s="32">
         <f t="shared" si="21"/>
-        <v>1750</v>
-      </c>
-      <c r="Q91" s="32">
+        <v>224069134598000</v>
+      </c>
+      <c r="R91" s="33">
         <f t="shared" si="22"/>
-        <v>224069134598000</v>
-      </c>
-      <c r="R91" s="33">
+        <v>89627653839200</v>
+      </c>
+      <c r="S91">
         <f t="shared" si="17"/>
         <v>89627653839200</v>
       </c>
-      <c r="S91">
+      <c r="T91" s="36">
         <f t="shared" si="18"/>
-        <v>89627653839200</v>
-      </c>
-      <c r="T91" s="36">
-        <f t="shared" si="19"/>
         <v>8962.7653839199993</v>
       </c>
       <c r="U91" t="s">
@@ -12962,27 +13204,26 @@
         <v>0.9</v>
       </c>
       <c r="F92">
-        <v>900</v>
+        <v>850</v>
       </c>
       <c r="G92">
-        <f t="shared" si="12"/>
         <v>800</v>
       </c>
       <c r="H92" s="32">
-        <f t="shared" si="20"/>
-        <v>93135110639200</v>
+        <f t="shared" si="19"/>
+        <v>45567555319600</v>
       </c>
       <c r="I92" s="33">
         <f t="shared" si="13"/>
-        <v>37254044255680</v>
+        <v>18227022127840</v>
       </c>
       <c r="J92">
         <f t="shared" si="14"/>
-        <v>22352426553408</v>
+        <v>18227022127840</v>
       </c>
       <c r="K92" s="36">
         <f t="shared" si="15"/>
-        <v>2235.2426553408</v>
+        <v>18227.022127839999</v>
       </c>
       <c r="M92">
         <v>5000</v>
@@ -12995,23 +13236,23 @@
         <v>2250</v>
       </c>
       <c r="P92">
+        <f t="shared" si="20"/>
+        <v>2000</v>
+      </c>
+      <c r="Q92" s="32">
         <f t="shared" si="21"/>
-        <v>2000</v>
-      </c>
-      <c r="Q92" s="32">
+        <v>250319134598000</v>
+      </c>
+      <c r="R92" s="33">
         <f t="shared" si="22"/>
-        <v>250319134598000</v>
-      </c>
-      <c r="R92" s="33">
+        <v>100127653839200</v>
+      </c>
+      <c r="S92">
         <f t="shared" si="17"/>
         <v>100127653839200</v>
       </c>
-      <c r="S92">
+      <c r="T92" s="36">
         <f t="shared" si="18"/>
-        <v>100127653839200</v>
-      </c>
-      <c r="T92" s="36">
-        <f t="shared" si="19"/>
         <v>10012.765383919999</v>
       </c>
       <c r="V92">
@@ -13026,27 +13267,26 @@
         <v>1</v>
       </c>
       <c r="F93">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="G93">
-        <f t="shared" si="12"/>
         <v>900</v>
       </c>
       <c r="H93" s="32">
-        <f t="shared" si="20"/>
-        <v>101135110639200</v>
+        <f t="shared" si="19"/>
+        <v>49567555319600</v>
       </c>
       <c r="I93" s="33">
         <f t="shared" si="13"/>
-        <v>40454044255680</v>
+        <v>19827022127840</v>
       </c>
       <c r="J93">
         <f t="shared" si="14"/>
-        <v>24272426553408</v>
+        <v>19827022127840</v>
       </c>
       <c r="K93" s="36">
         <f t="shared" si="15"/>
-        <v>2427.2426553408</v>
+        <v>19827.022127839999</v>
       </c>
       <c r="M93">
         <v>5000</v>
@@ -13059,23 +13299,23 @@
         <v>2500</v>
       </c>
       <c r="P93">
+        <f t="shared" si="20"/>
+        <v>2250</v>
+      </c>
+      <c r="Q93" s="32">
         <f t="shared" si="21"/>
-        <v>2250</v>
-      </c>
-      <c r="Q93" s="32">
+        <v>276569134598000</v>
+      </c>
+      <c r="R93" s="33">
         <f t="shared" si="22"/>
-        <v>276569134598000</v>
-      </c>
-      <c r="R93" s="33">
+        <v>110627653839200</v>
+      </c>
+      <c r="S93">
         <f t="shared" si="17"/>
         <v>110627653839200</v>
       </c>
-      <c r="S93">
+      <c r="T93" s="36">
         <f t="shared" si="18"/>
-        <v>110627653839200</v>
-      </c>
-      <c r="T93" s="36">
-        <f t="shared" si="19"/>
         <v>11062.765383919999</v>
       </c>
       <c r="V93">
@@ -13095,23 +13335,23 @@
         <v>2750</v>
       </c>
       <c r="P94">
+        <f t="shared" si="20"/>
+        <v>2500</v>
+      </c>
+      <c r="Q94" s="32">
         <f t="shared" si="21"/>
-        <v>2500</v>
-      </c>
-      <c r="Q94" s="32">
+        <v>302819134598000</v>
+      </c>
+      <c r="R94" s="33">
         <f t="shared" si="22"/>
-        <v>302819134598000</v>
-      </c>
-      <c r="R94" s="33">
+        <v>121127653839200</v>
+      </c>
+      <c r="S94">
         <f t="shared" si="17"/>
         <v>121127653839200</v>
       </c>
-      <c r="S94">
+      <c r="T94" s="36">
         <f t="shared" si="18"/>
-        <v>121127653839200</v>
-      </c>
-      <c r="T94" s="36">
-        <f t="shared" si="19"/>
         <v>12112.765383919999</v>
       </c>
       <c r="V94">
@@ -13132,23 +13372,23 @@
         <v>3000</v>
       </c>
       <c r="P95">
+        <f t="shared" si="20"/>
+        <v>2750</v>
+      </c>
+      <c r="Q95" s="32">
         <f t="shared" si="21"/>
-        <v>2750</v>
-      </c>
-      <c r="Q95" s="32">
+        <v>329069134598000</v>
+      </c>
+      <c r="R95" s="33">
         <f t="shared" si="22"/>
-        <v>329069134598000</v>
-      </c>
-      <c r="R95" s="33">
+        <v>131627653839200</v>
+      </c>
+      <c r="S95">
         <f t="shared" si="17"/>
         <v>131627653839200</v>
       </c>
-      <c r="S95">
+      <c r="T95" s="36">
         <f t="shared" si="18"/>
-        <v>131627653839200</v>
-      </c>
-      <c r="T95" s="36">
-        <f t="shared" si="19"/>
         <v>13162.765383919999</v>
       </c>
       <c r="U95" t="s">
@@ -13171,23 +13411,23 @@
         <v>3250</v>
       </c>
       <c r="P96">
+        <f t="shared" si="20"/>
+        <v>3000</v>
+      </c>
+      <c r="Q96" s="32">
         <f t="shared" si="21"/>
-        <v>3000</v>
-      </c>
-      <c r="Q96" s="32">
+        <v>355319134598000</v>
+      </c>
+      <c r="R96" s="33">
         <f t="shared" si="22"/>
-        <v>355319134598000</v>
-      </c>
-      <c r="R96" s="33">
+        <v>142127653839200</v>
+      </c>
+      <c r="S96">
         <f t="shared" si="17"/>
         <v>142127653839200</v>
       </c>
-      <c r="S96">
+      <c r="T96" s="36">
         <f t="shared" si="18"/>
-        <v>142127653839200</v>
-      </c>
-      <c r="T96" s="36">
-        <f t="shared" si="19"/>
         <v>14212.765383919999</v>
       </c>
       <c r="V96">
@@ -13208,23 +13448,23 @@
         <v>3500</v>
       </c>
       <c r="P97">
+        <f t="shared" si="20"/>
+        <v>3250</v>
+      </c>
+      <c r="Q97" s="32">
         <f t="shared" si="21"/>
-        <v>3250</v>
-      </c>
-      <c r="Q97" s="32">
+        <v>381569134598000</v>
+      </c>
+      <c r="R97" s="33">
         <f t="shared" si="22"/>
-        <v>381569134598000</v>
-      </c>
-      <c r="R97" s="33">
+        <v>152627653839200</v>
+      </c>
+      <c r="S97">
         <f t="shared" si="17"/>
         <v>152627653839200</v>
       </c>
-      <c r="S97">
+      <c r="T97" s="36">
         <f t="shared" si="18"/>
-        <v>152627653839200</v>
-      </c>
-      <c r="T97" s="36">
-        <f t="shared" si="19"/>
         <v>15262.765383919999</v>
       </c>
       <c r="V97">
@@ -13244,23 +13484,23 @@
         <v>3750</v>
       </c>
       <c r="P98">
+        <f t="shared" si="20"/>
+        <v>3500</v>
+      </c>
+      <c r="Q98" s="32">
         <f t="shared" si="21"/>
-        <v>3500</v>
-      </c>
-      <c r="Q98" s="32">
+        <v>407819134598000</v>
+      </c>
+      <c r="R98" s="33">
         <f t="shared" si="22"/>
-        <v>407819134598000</v>
-      </c>
-      <c r="R98" s="33">
+        <v>163127653839200</v>
+      </c>
+      <c r="S98">
         <f t="shared" si="17"/>
         <v>163127653839200</v>
       </c>
-      <c r="S98">
+      <c r="T98" s="36">
         <f t="shared" si="18"/>
-        <v>163127653839200</v>
-      </c>
-      <c r="T98" s="36">
-        <f t="shared" si="19"/>
         <v>16312.765383919999</v>
       </c>
       <c r="V98">
@@ -13281,23 +13521,23 @@
         <v>4000</v>
       </c>
       <c r="P99">
+        <f t="shared" si="20"/>
+        <v>3750</v>
+      </c>
+      <c r="Q99" s="32">
         <f t="shared" si="21"/>
-        <v>3750</v>
-      </c>
-      <c r="Q99" s="32">
+        <v>434069134598000</v>
+      </c>
+      <c r="R99" s="33">
         <f t="shared" si="22"/>
-        <v>434069134598000</v>
-      </c>
-      <c r="R99" s="33">
+        <v>173627653839200</v>
+      </c>
+      <c r="S99">
         <f t="shared" si="17"/>
         <v>173627653839200</v>
       </c>
-      <c r="S99">
+      <c r="T99" s="36">
         <f t="shared" si="18"/>
-        <v>173627653839200</v>
-      </c>
-      <c r="T99" s="36">
-        <f t="shared" si="19"/>
         <v>17362.765383919999</v>
       </c>
       <c r="U99" t="s">
@@ -13320,23 +13560,23 @@
         <v>4250</v>
       </c>
       <c r="P100">
+        <f t="shared" si="20"/>
+        <v>4000</v>
+      </c>
+      <c r="Q100" s="32">
         <f t="shared" si="21"/>
-        <v>4000</v>
-      </c>
-      <c r="Q100" s="32">
+        <v>460319134598000</v>
+      </c>
+      <c r="R100" s="33">
         <f t="shared" si="22"/>
-        <v>460319134598000</v>
-      </c>
-      <c r="R100" s="33">
+        <v>184127653839200</v>
+      </c>
+      <c r="S100">
         <f t="shared" si="17"/>
         <v>184127653839200</v>
       </c>
-      <c r="S100">
+      <c r="T100" s="36">
         <f t="shared" si="18"/>
-        <v>184127653839200</v>
-      </c>
-      <c r="T100" s="36">
-        <f t="shared" si="19"/>
         <v>18412.765383919999</v>
       </c>
       <c r="V100">
@@ -13357,23 +13597,23 @@
         <v>4500</v>
       </c>
       <c r="P101">
+        <f t="shared" si="20"/>
+        <v>4250</v>
+      </c>
+      <c r="Q101" s="32">
         <f t="shared" si="21"/>
-        <v>4250</v>
-      </c>
-      <c r="Q101" s="32">
+        <v>486569134598000</v>
+      </c>
+      <c r="R101" s="33">
         <f t="shared" si="22"/>
-        <v>486569134598000</v>
-      </c>
-      <c r="R101" s="33">
+        <v>194627653839200</v>
+      </c>
+      <c r="S101">
         <f t="shared" si="17"/>
         <v>194627653839200</v>
       </c>
-      <c r="S101">
+      <c r="T101" s="36">
         <f t="shared" si="18"/>
-        <v>194627653839200</v>
-      </c>
-      <c r="T101" s="36">
-        <f t="shared" si="19"/>
         <v>19462.765383919999</v>
       </c>
       <c r="V101">
@@ -13393,23 +13633,23 @@
         <v>4750</v>
       </c>
       <c r="P102">
+        <f t="shared" si="20"/>
+        <v>4500</v>
+      </c>
+      <c r="Q102" s="32">
         <f t="shared" si="21"/>
-        <v>4500</v>
-      </c>
-      <c r="Q102" s="32">
+        <v>512819134598000</v>
+      </c>
+      <c r="R102" s="33">
         <f t="shared" si="22"/>
-        <v>512819134598000</v>
-      </c>
-      <c r="R102" s="33">
+        <v>205127653839200</v>
+      </c>
+      <c r="S102">
         <f t="shared" si="17"/>
         <v>205127653839200</v>
       </c>
-      <c r="S102">
+      <c r="T102" s="36">
         <f t="shared" si="18"/>
-        <v>205127653839200</v>
-      </c>
-      <c r="T102" s="36">
-        <f t="shared" si="19"/>
         <v>20512.765383919999</v>
       </c>
       <c r="V102">
@@ -13430,23 +13670,23 @@
         <v>5000</v>
       </c>
       <c r="P103">
+        <f t="shared" si="20"/>
+        <v>4750</v>
+      </c>
+      <c r="Q103" s="32">
         <f t="shared" si="21"/>
-        <v>4750</v>
-      </c>
-      <c r="Q103" s="32">
+        <v>539069134598000</v>
+      </c>
+      <c r="R103" s="33">
         <f t="shared" si="22"/>
-        <v>539069134598000</v>
-      </c>
-      <c r="R103" s="33">
+        <v>215627653839200</v>
+      </c>
+      <c r="S103">
         <f t="shared" si="17"/>
         <v>215627653839200</v>
       </c>
-      <c r="S103">
+      <c r="T103" s="36">
         <f t="shared" si="18"/>
-        <v>215627653839200</v>
-      </c>
-      <c r="T103" s="36">
-        <f t="shared" si="19"/>
         <v>21562.765383919999</v>
       </c>
       <c r="V103">
@@ -13454,18 +13694,20 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="F80:I80"/>
-    <mergeCell ref="M80:Q80"/>
-    <mergeCell ref="F53:I53"/>
-    <mergeCell ref="M53:Q53"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G19:H19"/>
+  <mergeCells count="13">
+    <mergeCell ref="G24:H24"/>
     <mergeCell ref="N1:T1"/>
     <mergeCell ref="N11:T11"/>
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="F80:I80"/>
+    <mergeCell ref="M80:Q80"/>
+    <mergeCell ref="F53:I53"/>
+    <mergeCell ref="M53:Q53"/>
+    <mergeCell ref="G25:H25"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
